--- a/First Project/project/reports/clean_sales copy..xlsx
+++ b/First Project/project/reports/clean_sales copy..xlsx
@@ -5,26 +5,27 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kpada\OneDrive - ADvTECH Ltd\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kpada\OneDrive - ADvTECH Ltd\Desktop\sc_KaydenPadayachee_2026\First Project\project\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58018F3C-1310-4CEE-B774-7F4926BCBDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A0177B-A8F7-4167-86C2-E54B5D90A9F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FE0C601-E4F1-4E2F-88F8-1D17D8FD6B19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2FE0C601-E4F1-4E2F-88F8-1D17D8FD6B19}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="clean_sales" sheetId="1" r:id="rId2"/>
+    <sheet name="Pivot tables" sheetId="2" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId2"/>
+    <sheet name="clean_sales" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="33">
   <si>
     <t>transaction_id</t>
   </si>
@@ -606,7 +607,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -615,6 +616,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -687,8 +691,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[clean_sales copy..xlsx]Sheet1!PivotTable1</c:name>
-    <c:fmtId val="0"/>
+    <c:name>[clean_sales copy..xlsx]Pivot tables!PivotTable1</c:name>
+    <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -779,6 +783,118 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -791,7 +907,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$3</c:f>
+              <c:f>'Pivot tables'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -812,7 +928,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$4:$A$8</c:f>
+              <c:f>'Pivot tables'!$A$4:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -832,7 +948,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$8</c:f>
+              <c:f>'Pivot tables'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -853,7 +969,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C5BF-4877-B8F1-7D53B235637C}"/>
+              <c16:uniqueId val="{00000000-5AEF-42C1-9614-E9E25E92CE5F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1089,8 +1205,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[clean_sales copy..xlsx]Sheet1!PivotTable3</c:name>
-    <c:fmtId val="0"/>
+    <c:name>[clean_sales copy..xlsx]Pivot tables!PivotTable5</c:name>
+    <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1127,6 +1243,621 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot tables'!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0A61-433A-8922-8C9245DD7CFB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-0A61-433A-8922-8C9245DD7CFB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-0A61-433A-8922-8C9245DD7CFB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-0A61-433A-8922-8C9245DD7CFB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-0A61-433A-8922-8C9245DD7CFB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Pivot tables'!$O$4:$O$11</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="5"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Laptop</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Phone</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Tablet</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Chair</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Desk</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Electronics</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Furniture</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot tables'!$P$4:$P$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>180000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>440000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-0A61-433A-8922-8C9245DD7CFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[clean_sales copy..xlsx]Pivot tables!PivotTable3</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
@@ -1192,7 +1923,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$3</c:f>
+              <c:f>'Pivot tables'!$L$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1215,7 +1946,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$4:$K$8</c:f>
+              <c:f>'Pivot tables'!$K$4:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1235,7 +1966,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$4:$L$8</c:f>
+              <c:f>'Pivot tables'!$L$4:$L$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1257,7 +1988,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC03-4285-B96B-3469EE7754BC}"/>
+              <c16:uniqueId val="{00000000-108F-4DE1-BB26-8B6A6A992873}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1380,308 +2111,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[clean_sales copy..xlsx]Sheet1!PivotTable5</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$P$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$O$4:$O$6</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Furniture</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$P$4:$P$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>770000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>133500</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1F21-42A3-9F33-707E7AF83C6B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2407,522 +2836,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3441,27 +3354,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>590177</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>19052</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>25401</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4797</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>197223</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8509F0E6-E961-0481-F42E-B182D90BB98E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1406106-911B-DC6B-BA94-4B55E08652C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3481,23 +3910,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>255494</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>26895</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25399</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>7140</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>80683</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="3" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBF8FDF4-F130-E3D1-E956-61F83F993F6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DCBFF3A-B529-3FAC-82D8-2C4E9BB009A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3517,23 +3946,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>791135</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>56030</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>25401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>737347</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>109818</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>33283</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="4" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF45ECBF-EA24-B6B4-5AEF-4F08E0C591F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922BED21-4B2C-FED6-D330-3D35ACB0FE30}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,7 +4011,16 @@
       </sharedItems>
     </cacheField>
     <cacheField name="quantity" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7" count="8">
+        <n v="2"/>
+        <n v="5"/>
+        <n v="3"/>
+        <n v="0"/>
+        <n v="1"/>
+        <n v="6"/>
+        <n v="4"/>
+        <n v="7"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="price" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1500" maxValue="12000"/>
@@ -4028,7 +4466,7 @@
     <d v="2024-01-05T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="12000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4040,7 +4478,7 @@
     <d v="2024-01-07T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="8000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4052,7 +4490,7 @@
     <d v="2024-01-10T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="6000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4064,7 +4502,7 @@
     <d v="2024-01-15T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="0"/>
+    <x v="3"/>
     <n v="1500"/>
     <x v="3"/>
     <x v="3"/>
@@ -4076,7 +4514,7 @@
     <d v="2024-01-20T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="3000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4088,7 +4526,7 @@
     <d v="2024-01-22T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="4"/>
     <n v="12000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4100,7 +4538,7 @@
     <d v="2024-01-25T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="6"/>
+    <x v="5"/>
     <n v="8000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4112,7 +4550,7 @@
     <d v="2024-01-28T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="6000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4124,7 +4562,7 @@
     <d v="2024-02-01T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="1500"/>
     <x v="0"/>
     <x v="0"/>
@@ -4136,7 +4574,7 @@
     <d v="2024-02-03T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="3000"/>
     <x v="1"/>
     <x v="4"/>
@@ -4148,7 +4586,7 @@
     <d v="2024-02-05T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="12000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4160,7 +4598,7 @@
     <d v="2024-02-07T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="4"/>
+    <x v="6"/>
     <n v="8000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4172,7 +4610,7 @@
     <d v="2024-02-10T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="6000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4184,7 +4622,7 @@
     <d v="2024-02-12T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="6"/>
+    <x v="5"/>
     <n v="1500"/>
     <x v="1"/>
     <x v="1"/>
@@ -4196,7 +4634,7 @@
     <d v="2024-02-15T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="3000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4208,7 +4646,7 @@
     <d v="2024-02-18T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="4"/>
     <n v="12000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4220,7 +4658,7 @@
     <d v="2024-02-20T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="7"/>
+    <x v="7"/>
     <n v="8000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4232,7 +4670,7 @@
     <d v="2024-02-22T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="6000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4244,7 +4682,7 @@
     <d v="2024-02-25T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="4"/>
+    <x v="6"/>
     <n v="1500"/>
     <x v="2"/>
     <x v="2"/>
@@ -4256,7 +4694,7 @@
     <d v="2024-02-28T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="3000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4268,7 +4706,7 @@
     <d v="2024-03-02T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="12000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4280,7 +4718,7 @@
     <d v="2024-03-04T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="8000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4292,7 +4730,7 @@
     <d v="2024-03-06T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="6000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4304,7 +4742,7 @@
     <d v="2024-03-08T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="4"/>
+    <x v="6"/>
     <n v="1500"/>
     <x v="3"/>
     <x v="3"/>
@@ -4316,7 +4754,7 @@
     <d v="2024-03-10T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="3000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4328,7 +4766,7 @@
     <d v="2024-03-12T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="4"/>
     <n v="12000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4340,7 +4778,7 @@
     <d v="2024-03-14T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="6"/>
+    <x v="5"/>
     <n v="8000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4352,7 +4790,7 @@
     <d v="2024-03-16T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="6000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4364,7 +4802,7 @@
     <d v="2024-03-18T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="1500"/>
     <x v="0"/>
     <x v="0"/>
@@ -4376,7 +4814,7 @@
     <d v="2024-03-20T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="3000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4388,7 +4826,7 @@
     <d v="2024-03-22T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="12000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4400,7 +4838,7 @@
     <d v="2024-03-24T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="4"/>
+    <x v="6"/>
     <n v="8000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4412,7 +4850,7 @@
     <d v="2024-03-26T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="6000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4424,7 +4862,7 @@
     <d v="2024-03-28T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="6"/>
+    <x v="5"/>
     <n v="1500"/>
     <x v="1"/>
     <x v="1"/>
@@ -4436,7 +4874,7 @@
     <d v="2024-03-30T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="3000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4448,7 +4886,7 @@
     <d v="2024-04-02T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="4"/>
     <n v="12000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4460,7 +4898,7 @@
     <d v="2024-04-04T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="7"/>
+    <x v="7"/>
     <n v="8000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4472,7 +4910,7 @@
     <d v="2024-04-06T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="6000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4484,7 +4922,7 @@
     <d v="2024-04-08T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="4"/>
+    <x v="6"/>
     <n v="1500"/>
     <x v="2"/>
     <x v="2"/>
@@ -4496,7 +4934,7 @@
     <d v="2024-04-10T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="3000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4508,7 +4946,7 @@
     <d v="2024-04-12T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="12000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4520,7 +4958,7 @@
     <d v="2024-04-14T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="8000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4532,7 +4970,7 @@
     <d v="2024-04-16T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="6000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4544,7 +4982,7 @@
     <d v="2024-04-18T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="0"/>
+    <x v="3"/>
     <n v="1500"/>
     <x v="3"/>
     <x v="3"/>
@@ -4556,7 +4994,7 @@
     <d v="2024-04-20T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="3000"/>
     <x v="0"/>
     <x v="0"/>
@@ -4568,7 +5006,7 @@
     <d v="2024-04-22T00:00:00"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="4"/>
     <n v="12000"/>
     <x v="1"/>
     <x v="4"/>
@@ -4580,7 +5018,7 @@
     <d v="2024-04-24T00:00:00"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="6"/>
+    <x v="5"/>
     <n v="8000"/>
     <x v="2"/>
     <x v="2"/>
@@ -4592,7 +5030,7 @@
     <d v="2024-04-26T00:00:00"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="6000"/>
     <x v="3"/>
     <x v="3"/>
@@ -4604,7 +5042,7 @@
     <d v="2024-04-28T00:00:00"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="5"/>
+    <x v="1"/>
     <n v="1500"/>
     <x v="0"/>
     <x v="0"/>
@@ -4616,7 +5054,7 @@
     <d v="2024-04-30T00:00:00"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="3000"/>
     <x v="1"/>
     <x v="1"/>
@@ -4627,12 +5065,21 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECE792C6-4CB2-4E29-AC3C-9FB1959C3A99}" name="PivotTable5" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="O3:P6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECE792C6-4CB2-4E29-AC3C-9FB1959C3A99}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="O3:P11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
@@ -4674,14 +5121,30 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="2">
     <field x="3"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="8">
     <i>
       <x/>
     </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
     <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
       <x v="1"/>
     </i>
     <i t="grand">
@@ -4694,12 +5157,87 @@
   <dataFields count="1">
     <dataField name="Sum of revenue" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+  <chartFormats count="6">
+    <chartFormat chart="3" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -4718,13 +5256,28 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91871137-E73C-4170-B018-A71FA37AF8F7}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91871137-E73C-4170-B018-A71FA37AF8F7}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A31:B47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -4768,24 +5321,55 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="2">
     <field x="7"/>
+    <field x="3"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="16">
     <i>
       <x/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i>
       <x v="3"/>
     </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i>
       <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -4810,7 +5394,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAD55AD1-D415-4985-830C-5CFA0117B651}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAD55AD1-D415-4985-830C-5CFA0117B651}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="K3:L8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5253,7 +5837,7 @@
     <dataField name="Sum of revenue" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="2" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5276,7 +5860,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E9AEEBC-6C6C-470D-B595-DAB9E70CBBCA}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E9AEEBC-6C6C-470D-B595-DAB9E70CBBCA}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G3:H9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5741,7 +6325,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5663AEB1-E935-404B-AA93-AEE50E451945}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5663AEB1-E935-404B-AA93-AEE50E451945}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -6190,7 +6774,7 @@
     <dataField name="Sum of revenue" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="2" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6529,18 +7113,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1374B7D5-52CE-4278-BCB2-B32A2AA568C9}">
-  <dimension ref="A3:P18"/>
+  <dimension ref="A3:P47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="1" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.33203125" customWidth="1"/>
     <col min="7" max="7" width="17.44140625" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.5546875" customWidth="1"/>
     <col min="12" max="12" width="21.77734375" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="18.5546875" customWidth="1"/>
+    <col min="15" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -6579,13 +7162,13 @@
       <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>58500</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>160000</v>
       </c>
       <c r="O4" s="4" t="s">
@@ -6605,20 +7188,20 @@
       <c r="G5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>75000</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>200500</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>21</v>
+      <c r="O5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="P5" s="5">
-        <v>133500</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -6631,20 +7214,20 @@
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>180000</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>271500</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>27</v>
+      <c r="O6" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="P6" s="5">
-        <v>903500</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -6657,14 +7240,20 @@
       <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>440000</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>271500</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="5">
+        <v>150000</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -6677,87 +7266,204 @@
       <c r="G8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>150000</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>903500</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="5">
+        <v>133500</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>903500</v>
       </c>
+      <c r="O9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P9" s="5">
+        <v>58500</v>
+      </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="5">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="5">
+        <v>903500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B32" s="5">
         <v>270000</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="5">
+        <v>246000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="5">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B35" s="5">
         <v>260500</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="5">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="5">
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B38" s="5">
         <v>204000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="5">
+        <v>168000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="5">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B41" s="5">
         <v>21000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="5">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="5">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B44" s="5">
         <v>148000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="5">
+        <v>124000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="5">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B47" s="5">
         <v>903500</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE53B7F-BDD3-4CCC-99A7-2B974AAE7264}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C90561-1EE5-4BEC-B3E1-BCA9919D2F57}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
